--- a/artfynd/A 27866-2024 artfynd.xlsx
+++ b/artfynd/A 27866-2024 artfynd.xlsx
@@ -1567,12 +1567,7 @@
         <v>74434227</v>
       </c>
       <c r="B9" t="n">
-        <v>103365</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105744</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,10 +1599,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527281.2870873421</v>
+        <v>527281</v>
       </c>
       <c r="R9" t="n">
-        <v>6316887.523718655</v>
+        <v>6316888</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1637,19 +1632,9 @@
           <t>2001-09-15</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2001-09-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1693,12 +1678,7 @@
         <v>75061747</v>
       </c>
       <c r="B10" t="n">
-        <v>102161</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1730,10 +1710,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527281.2870873421</v>
+        <v>527281</v>
       </c>
       <c r="R10" t="n">
-        <v>6316887.523718655</v>
+        <v>6316888</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1763,19 +1743,9 @@
           <t>2001-09-15</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2001-09-15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">

--- a/artfynd/A 27866-2024 artfynd.xlsx
+++ b/artfynd/A 27866-2024 artfynd.xlsx
@@ -1567,7 +1567,7 @@
         <v>74434227</v>
       </c>
       <c r="B9" t="n">
-        <v>105744</v>
+        <v>105753</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>75061747</v>
       </c>
       <c r="B10" t="n">
-        <v>104532</v>
+        <v>104541</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27866-2024 artfynd.xlsx
+++ b/artfynd/A 27866-2024 artfynd.xlsx
@@ -1567,7 +1567,7 @@
         <v>74434227</v>
       </c>
       <c r="B9" t="n">
-        <v>105753</v>
+        <v>105758</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>75061747</v>
       </c>
       <c r="B10" t="n">
-        <v>104541</v>
+        <v>104544</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27866-2024 artfynd.xlsx
+++ b/artfynd/A 27866-2024 artfynd.xlsx
@@ -1567,7 +1567,7 @@
         <v>74434227</v>
       </c>
       <c r="B9" t="n">
-        <v>105758</v>
+        <v>105786</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>75061747</v>
       </c>
       <c r="B10" t="n">
-        <v>104544</v>
+        <v>104571</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27866-2024 artfynd.xlsx
+++ b/artfynd/A 27866-2024 artfynd.xlsx
@@ -1567,7 +1567,7 @@
         <v>74434227</v>
       </c>
       <c r="B9" t="n">
-        <v>105786</v>
+        <v>105792</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>75061747</v>
       </c>
       <c r="B10" t="n">
-        <v>104571</v>
+        <v>104577</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27866-2024 artfynd.xlsx
+++ b/artfynd/A 27866-2024 artfynd.xlsx
@@ -1567,7 +1567,7 @@
         <v>74434227</v>
       </c>
       <c r="B9" t="n">
-        <v>105792</v>
+        <v>105799</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>75061747</v>
       </c>
       <c r="B10" t="n">
-        <v>104577</v>
+        <v>104584</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27866-2024 artfynd.xlsx
+++ b/artfynd/A 27866-2024 artfynd.xlsx
@@ -1567,7 +1567,7 @@
         <v>74434227</v>
       </c>
       <c r="B9" t="n">
-        <v>105799</v>
+        <v>105803</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>75061747</v>
       </c>
       <c r="B10" t="n">
-        <v>104584</v>
+        <v>104588</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27866-2024 artfynd.xlsx
+++ b/artfynd/A 27866-2024 artfynd.xlsx
@@ -1567,7 +1567,7 @@
         <v>74434227</v>
       </c>
       <c r="B9" t="n">
-        <v>105803</v>
+        <v>105810</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>75061747</v>
       </c>
       <c r="B10" t="n">
-        <v>104588</v>
+        <v>104595</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27866-2024 artfynd.xlsx
+++ b/artfynd/A 27866-2024 artfynd.xlsx
@@ -1567,7 +1567,7 @@
         <v>74434227</v>
       </c>
       <c r="B9" t="n">
-        <v>105813</v>
+        <v>105818</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>75061747</v>
       </c>
       <c r="B10" t="n">
-        <v>104598</v>
+        <v>104603</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27866-2024 artfynd.xlsx
+++ b/artfynd/A 27866-2024 artfynd.xlsx
@@ -1567,7 +1567,7 @@
         <v>74434227</v>
       </c>
       <c r="B9" t="n">
-        <v>105818</v>
+        <v>105826</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>75061747</v>
       </c>
       <c r="B10" t="n">
-        <v>104603</v>
+        <v>104611</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27866-2024 artfynd.xlsx
+++ b/artfynd/A 27866-2024 artfynd.xlsx
@@ -1567,7 +1567,7 @@
         <v>74434227</v>
       </c>
       <c r="B9" t="n">
-        <v>105826</v>
+        <v>105836</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>75061747</v>
       </c>
       <c r="B10" t="n">
-        <v>104611</v>
+        <v>104621</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27866-2024 artfynd.xlsx
+++ b/artfynd/A 27866-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13369008</v>
+        <v>221764</v>
       </c>
       <c r="B2" t="n">
-        <v>27695</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101766</v>
+        <v>673</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelörtskinnbagge</t>
+          <t>Backmåra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Canthophorus impressus</t>
+          <t>Galium suecicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Horváth, 1881)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+          <t>(Sterner) Ehrend.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skahus barktipp, Sm</t>
+          <t>Sävsjö (Skahus 200 m NO), Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527293.3013657246</v>
+        <v>527275</v>
       </c>
       <c r="R2" t="n">
-        <v>6316886.513274265</v>
+        <v>6316822</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,24 +738,19 @@
           <t>Lenhovda</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>G-Upp-0007</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2007-06-29</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1991-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2007-06-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1991-12-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,33 +764,32 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>gammal barktipp</t>
+          <t>Torr gräsmark</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>G-län Floraväktarna</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Kerstin Petersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>13369004</v>
+        <v>74434227</v>
       </c>
       <c r="B3" t="n">
-        <v>27695</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,46 +797,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101766</v>
+        <v>673</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelörtskinnbagge</t>
+          <t>Backmåra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Canthophorus impressus</t>
+          <t>Galium suecicum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Horváth, 1881)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>(Sterner) Ehrend.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skahus, Sm</t>
+          <t>Skahus 200 m NO, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527249.871541712</v>
+        <v>527281</v>
       </c>
       <c r="R3" t="n">
-        <v>6316850.821481211</v>
+        <v>6316888</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,22 +851,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2007-06-27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2001-09-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2007-06-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2001-09-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 5F3f 3733. SOM: Galium suecicum. LEG: KP &amp; Stefan Nilsson. KOM: 3 m²</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,33 +875,32 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>gammal väg till barktipp</t>
+          <t>Torr gräsmark</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>593885</v>
+        <v>593883</v>
       </c>
       <c r="B4" t="n">
-        <v>102160</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,7 +927,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -976,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527249.871541712</v>
+        <v>527255</v>
       </c>
       <c r="R4" t="n">
-        <v>6316850.821481211</v>
+        <v>6316824</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,21 +974,11 @@
           <t>2007-06-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2007-06-27</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1040,7 +995,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>gammal väg till barktipp</t>
+          <t>vägkant</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1058,15 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>593894</v>
+        <v>593884</v>
       </c>
       <c r="B5" t="n">
-        <v>102160</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1103,17 +1053,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skahus barktipp, Sm</t>
+          <t>Skahus, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527293.3013657246</v>
+        <v>527275</v>
       </c>
       <c r="R5" t="n">
-        <v>6316886.513274265</v>
+        <v>6316822</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1137,22 +1087,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2007-06-29</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-06-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2007-06-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-06-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1171,7 +1111,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>gammal barktipp</t>
+          <t>vägkant</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1189,15 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>13380584</v>
+        <v>593885</v>
       </c>
       <c r="B6" t="n">
-        <v>12722</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,37 +1140,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105845</v>
+        <v>1560</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spindelört</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Uloma rufa</t>
+          <t>Thesium alpinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Piller &amp; Mitterpacher, 1783)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skahus barktipp, Sm</t>
+          <t>Skahus, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527293.3013657246</v>
+        <v>527250</v>
       </c>
       <c r="R6" t="n">
-        <v>6316886.513274265</v>
+        <v>6316851</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1259,22 +1203,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2007-06-29</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-06-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2007-06-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-06-27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1286,12 +1220,16 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Artificiell miljö</t>
+        </is>
+      </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>gammal barktipp</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr"/>
+          <t>gammal väg till barktipp</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
@@ -1307,15 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>596884</v>
+        <v>593894</v>
       </c>
       <c r="B7" t="n">
-        <v>102161</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1275,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1356,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527294.4000852404</v>
+        <v>527293</v>
       </c>
       <c r="R7" t="n">
-        <v>6316885.431073821</v>
+        <v>6316887</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1386,22 +1319,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2011-06-27</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-06-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2011-06-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-06-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1415,38 +1338,33 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Konstruerad mark</t>
+          <t>Artificiell miljö</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Gammal barktipp</t>
+          <t>gammal barktipp</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>14936219</v>
+        <v>594097</v>
       </c>
       <c r="B8" t="n">
-        <v>27696</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105117</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,26 +1372,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101766</v>
+        <v>1560</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelörtskinnbagge</t>
+          <t>Spindelört</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Canthophorus impressus</t>
+          <t>Thesium alpinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Horváth, 1881)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1482,13 +1405,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527294.4000852404</v>
+        <v>527272</v>
       </c>
       <c r="R8" t="n">
-        <v>6316885.431073821</v>
+        <v>6316825</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1512,27 +1435,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2011-06-27</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-06-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2011-06-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>7 imago, 132 nymfer</t>
+          <t>2007-06-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1544,30 +1452,35 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Ruderatmark</t>
+        </is>
+      </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Gammal barktipp</t>
+          <t>gammal körväg</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>74434227</v>
+        <v>596884</v>
       </c>
       <c r="B9" t="n">
-        <v>105836</v>
+        <v>105117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,37 +1488,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>673</v>
+        <v>1560</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Backmåra</t>
+          <t>Spindelört</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Galium suecicum</t>
+          <t>Thesium alpinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sterner) Ehrend.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skahus 200 m NO, Sm</t>
+          <t>Skahus barktipp, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527281</v>
+        <v>527294</v>
       </c>
       <c r="R9" t="n">
-        <v>6316888</v>
+        <v>6316885</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1629,17 +1551,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2001-09-15</t>
+          <t>2011-06-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2001-09-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 5F3f 3733. SOM: Galium suecicum. LEG: KP &amp; Stefan Nilsson. KOM: 3 m²</t>
+          <t>2011-06-27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1651,34 +1568,35 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Konstruerad mark</t>
+        </is>
+      </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Torr gräsmark</t>
+          <t>Gammal barktipp</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Sofia Lundman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>75061747</v>
       </c>
       <c r="B10" t="n">
-        <v>104621</v>
+        <v>105116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1783,6 +1701,339 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>13369004</v>
+      </c>
+      <c r="B11" t="n">
+        <v>26894</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>101766</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spindelörtskinnbagge</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Canthophorus impressus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Horváth, 1881)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skahus, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>527250</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6316851</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lenhovda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2007-06-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2007-06-27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>gammal väg till barktipp</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>13369008</v>
+      </c>
+      <c r="B12" t="n">
+        <v>26894</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>101766</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spindelörtskinnbagge</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Canthophorus impressus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Horváth, 1881)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skahus barktipp, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>527293</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6316887</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lenhovda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2007-06-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2007-06-29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>gammal barktipp</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>14936219</v>
+      </c>
+      <c r="B13" t="n">
+        <v>26894</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>101766</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spindelörtskinnbagge</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Canthophorus impressus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Horváth, 1881)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skahus barktipp, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>527294</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6316885</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lenhovda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2011-06-27</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2011-06-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>7 imago, 132 nymfer</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Gammal barktipp</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
